--- a/Conference_tracker_list.xlsx
+++ b/Conference_tracker_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/Bureau/Conference tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{2519A65A-8458-4AEA-A976-110AA28DBE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E04292-160B-44E7-AA26-7C38FB4147D0}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{2519A65A-8458-4AEA-A976-110AA28DBE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E31C0A2-D794-4DFC-93AF-0A9943600484}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{34AF357E-1D98-491C-93AB-F4960DB608EF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{34AF357E-1D98-491C-93AB-F4960DB608EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
   <si>
     <t>Conference</t>
   </si>
@@ -143,9 +143,6 @@
     <t>International Neurological Physiotherapy Association</t>
   </si>
   <si>
-    <t>https://inpa.world/global-conference/</t>
-  </si>
-  <si>
     <t>RASEN</t>
   </si>
   <si>
@@ -230,9 +227,6 @@
     <t>Academy of Neurologic Physical Therapy</t>
   </si>
   <si>
-    <t>https://www.neuropt.org/</t>
-  </si>
-  <si>
     <t>APTA</t>
   </si>
   <si>
@@ -249,16 +243,36 @@
   </si>
   <si>
     <t>https://congresoaef.com/</t>
+  </si>
+  <si>
+    <t>https://www.neuropt.org/education---conferences/apta-conference</t>
+  </si>
+  <si>
+    <t>https://inpa.world/global-conference/conference-details/</t>
+  </si>
+  <si>
+    <t>RehabWeek</t>
+  </si>
+  <si>
+    <t>https://rehabweek.org/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -281,13 +295,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -624,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1054293E-2AAA-42CD-933D-A2F4C6AE3D2C}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.08984375" customWidth="1"/>
@@ -650,7 +667,7 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -661,7 +678,7 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -672,7 +689,7 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -683,7 +700,7 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -694,7 +711,7 @@
       <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -705,7 +722,7 @@
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -716,7 +733,7 @@
       <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -727,7 +744,7 @@
       <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -738,7 +755,7 @@
       <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -749,7 +766,7 @@
       <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -760,144 +777,181 @@
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
-        <v>35</v>
+      <c r="C12" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
         <v>56</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
         <v>59</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
         <v>62</v>
       </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>64</v>
+      <c r="C22" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>70</v>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{B8EC1577-8A92-4840-BA4E-7EB8820E1146}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{A6D21793-C7BB-4899-A322-FC846F46C7A1}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{03F4E362-FBA8-44A2-836D-B5E2EACD3843}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{2B5642DE-8A05-4FBC-BC45-07A3CC926E87}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{3CA58615-6623-47C1-80F3-2AEE1EAE5B98}"/>
+    <hyperlink ref="C2" r:id="rId6" xr:uid="{8FE7F80B-A200-4D2C-B369-E713515E41B6}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{3A67BAC8-2D70-4DE3-BF9C-57A08CC12C72}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{91AFF677-1DBE-4C26-B847-163551D01CA8}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{CE239A7C-CA38-4EF4-BFA6-F99F51F846CC}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{67FE98C6-C25D-4C45-B22B-563ADA2548AF}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{1EFCFBBE-D4AC-4AAA-A60C-28B0E92C9903}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{261EF938-1729-421D-B809-FDD610BE62FA}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{E085EA87-115C-4F2A-ABE5-16B14E25165B}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{9C8A527E-BF57-4BF8-B207-535695FBBC03}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{742F6DB5-40DB-4804-B8B3-588B7A579223}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{D0F5BC8D-32F0-4FFD-9B05-748BF4AD7074}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{3EA5EB4E-4872-46D8-9C03-AFCA41B7F865}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{3B0D3C25-68FF-485F-9855-4618CC85516E}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{3577BDE1-FE3C-47DB-A603-F830277B0FC3}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{7DE9678A-7E5F-464D-A036-84370E19C247}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{2E1B5A87-1C2B-4BCF-A226-48EA5D33DFCD}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{01EA497A-F370-4FF4-B07E-7A06F455D110}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{B108C314-DEFF-43E4-8337-8DCFFF000225}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{AA88FA37-0645-47C5-A066-F565ABD8C76D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
--- a/Conference_tracker_list.xlsx
+++ b/Conference_tracker_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/Bureau/Conference tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{2519A65A-8458-4AEA-A976-110AA28DBE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E31C0A2-D794-4DFC-93AF-0A9943600484}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="8_{2519A65A-8458-4AEA-A976-110AA28DBE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFF9240E-D28B-4B22-AB8D-A3896B784D9C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{34AF357E-1D98-491C-93AB-F4960DB608EF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
   <si>
     <t>Conference</t>
   </si>
@@ -255,6 +255,15 @@
   </si>
   <si>
     <t>https://rehabweek.org/</t>
+  </si>
+  <si>
+    <t>ISC</t>
+  </si>
+  <si>
+    <t>American Heart Association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://professional.heart.org/en/meetings/international-stroke-conference </t>
   </si>
 </sst>
 </file>
@@ -641,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1054293E-2AAA-42CD-933D-A2F4C6AE3D2C}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.08984375" customWidth="1"/>
@@ -922,6 +931,17 @@
       </c>
       <c r="C25" s="1" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -950,8 +970,9 @@
     <hyperlink ref="C23" r:id="rId22" xr:uid="{01EA497A-F370-4FF4-B07E-7A06F455D110}"/>
     <hyperlink ref="C24" r:id="rId23" xr:uid="{B108C314-DEFF-43E4-8337-8DCFFF000225}"/>
     <hyperlink ref="C25" r:id="rId24" xr:uid="{AA88FA37-0645-47C5-A066-F565ABD8C76D}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{5E8AF961-858F-4F4A-9D5B-012A71DA904F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>